--- a/artfynd/A 43647-2025 artfynd.xlsx
+++ b/artfynd/A 43647-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121616845</v>
+        <v>121616846</v>
       </c>
       <c r="B2" t="n">
-        <v>90744</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121616846</v>
+        <v>121616853</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,12 +796,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572525</v>
+        <v>572515</v>
       </c>
       <c r="R3" t="n">
-        <v>6853471</v>
+        <v>6853496</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121616841</v>
+        <v>121616845</v>
       </c>
       <c r="B4" t="n">
-        <v>90709</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572567</v>
+        <v>572525</v>
       </c>
       <c r="R4" t="n">
-        <v>6853446</v>
+        <v>6853471</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121616866</v>
+        <v>121616848</v>
       </c>
       <c r="B5" t="n">
-        <v>90744</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572493</v>
+        <v>572507</v>
       </c>
       <c r="R5" t="n">
-        <v>6853491</v>
+        <v>6853486</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121616853</v>
+        <v>121616866</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572515</v>
+        <v>572493</v>
       </c>
       <c r="R6" t="n">
-        <v>6853496</v>
+        <v>6853491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121616833</v>
+        <v>121616892</v>
       </c>
       <c r="B7" t="n">
-        <v>90764</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572482</v>
+        <v>572404</v>
       </c>
       <c r="R7" t="n">
-        <v>6853601</v>
+        <v>6853548</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121616848</v>
+        <v>121616833</v>
       </c>
       <c r="B8" t="n">
-        <v>90744</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572507</v>
+        <v>572482</v>
       </c>
       <c r="R8" t="n">
-        <v>6853486</v>
+        <v>6853601</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,6 +1379,208 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121616841</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SV Tjärnmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>572567</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6853446</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Delsbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121616889</v>
+      </c>
+      <c r="B10" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SV Tjärnmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>572412</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6853533</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Delsbo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per-Gunnar Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
